--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="匹配设置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="决策表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="测试" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +65,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -86,11 +87,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -131,6 +165,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,215 +669,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>命中策略</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>首次命中</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>每行只听优先级数字最小的那条命中规则, 命中即停; 同优先级按行序。输出格 清空 = 写成空值, - = 不改</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>变量</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>定义</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>规则ID</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>拟任人有变化</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>本期.拟任人 != 上期.拟任人 或 (为空(上期.拟任人) 且 非空(本期.拟任人))</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>!= 两侧有空值就不成立 (和单元格一样), 所以「上期没填、本期填了」要单独写一支</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>规则ID</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>本期.类别-会议</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>上期.类别-会议</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>状态-会议</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>流程节点有变化</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>本期.流程节点 != 上期.流程节点 或 (为空(上期.流程节点) 且 非空(本期.流程节点))</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>同上。两期都空不算变化</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>为空</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>清空</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>本期不再上会, 清掉状态 (清空 = 写成空值; - 才是不改)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>近2个月酝酿及上会计划</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>酝酿中的岗位由人工维护, 不处理。首次命中 下命中即停, S3 / S4 不再看这一行 (优先级 策略下会被 S4 改成 01-新增)</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>连接词</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>= 本期.类别-会议</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>02-进展更新</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>类别与上期相同, 记为进展更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>01-新增</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>兜底: 前面都没命中的行 (有类别、不是酝酿、与上期不同) 都是新增</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>可用函数</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
         </is>
       </c>
     </row>
@@ -857,27 +770,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>命中策略</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>首次命中</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>每行只听优先级数字最小的那条命中规则, 命中即停; 同优先级按行序。输出格 清空 = 写成空值, - = 不改</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>规则ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>本期.类别-会议</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>上期.类别-会议</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>拟任人有变化</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>流程节点有变化</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>状态-会议</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>为空</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>清空</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>本期不再上会, 清掉状态 (清空 = 写成空值; - 才是不改)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>近2个月酝酿及上会计划</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>酝酿中的岗位由人工维护, 不处理。首次命中 下命中即停, 后面的规则不再看这一行 (优先级 策略下会被 S5 改成 01-新增)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>= 本期.类别-会议</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>类别与上期相同, 且拟任人或流程节点有变化。两行同一个规则ID = 同一条规则的两个「或」分支: 每行各格 AND, 行间 OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>= 本期.类别-会议</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>S3 的第二个分支。续行的优先级和输出留空 (或与首行相同), 规则ID 可以合并单元格</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>= 本期.类别-会议</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>03-按计划进行</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>类别与上期相同, 没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>兜底: 前面都没命中的行 (有类别、不是酝酿、与上期不同) 都是新增</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="64" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>用例</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>输入</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>期望</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>每行一个用例: 填输入变量的值, 期望列留空表示「该列不变」, 写 清空 表示「该列应为空」</t>
         </is>
       </c>
     </row>
@@ -889,114 +1204,162 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>输入</t>
+          <t>本期.类别-会议</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>输入</t>
+          <t>本期.状态-会议</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>期望</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
+          <t>上期.类别-会议</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>本期.拟任人</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>上期.拟任人</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>本期.流程节点</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>上期.流程节点</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>状态-会议</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>用例</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>本期.类别-会议</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>本期.状态-会议</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>上期.类别-会议</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>状态-会议</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>说明</t>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>清空</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>类别为空, 清掉状态。期望格写 清空 = 期望该列为空 (留空是期望不变)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>01-新增</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>变动通报</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>清空</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>类别为空, 清掉状态。期望格写 清空 = 期望该列为空 (留空是期望不变)</t>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>近2个月酝酿及上会计划</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>S2 拦截, 状态保持空; 优先级 策略下会被 S5 改成 01-新增, 这条用例会失败</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>近2个月酝酿及上会计划</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>S2 拦截, 状态保持空; 优先级 策略下会被 S4 改成 01-新增, 这条用例会失败</t>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>类别相同, 拟任人变了 -&gt; 进展更新</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1004,71 +1367,83 @@
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>变动通报</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>02-进展更新</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>类别与上期相同 -&gt; 进展更新</t>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>上期没有这个岗位 -&gt; 兜底新增</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>变动通报</t>
-        </is>
-      </c>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>01-新增</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>上期没有这个岗位 -&gt; 兜底新增</t>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>清空本来就空的格, 无变化</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>清空本来就空的格, 无变化</t>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>近2个月酝酿及上会计划</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>类别变了 -&gt; 重新计为新增</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1078,22 +1453,178 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>公司审批</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>近2个月酝酿及上会计划</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>类别相同, 流程节点变了 -&gt; S3 的第二个分支</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>周七</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>周七</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>公司审批</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>公司审批</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>03-按计划进行</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>类别相同, 都没变 -&gt; 按计划进行</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>类别变了 -&gt; 重新计为新增</t>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>上期拟任人为空、本期有 = 新任命, 算变化 (变量定义里显式写的那一支)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>03-按计划进行</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>两期拟任人都空不算变化: != 两侧有空值就不成立, 决策表与 YAML 一致</t>
         </is>
       </c>
     </row>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -153,6 +153,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -161,9 +164,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>本期.拟任人 != 上期.拟任人 或 (为空(上期.拟任人) 且 非空(本期.拟任人))</t>
+          <t>本期.拟任人 != 上期.拟任人 或 (上期.拟任人 == 空 且 本期.拟任人 != 空)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>!= 两侧有空值就不成立 (和单元格一样), 所以「上期没填、本期填了」要单独写一支</t>
+          <t>!= 两侧有空值就不成立 (和单元格一样), 所以「上期没填、本期填了」要单独写一支; == 空 / != 空 就是判空</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>本期.流程节点 != 上期.流程节点 或 (为空(上期.流程节点) 且 非空(本期.流程节点))</t>
+          <t>本期.流程节点 != 上期.流程节点 或 (上期.流程节点 == 空 且 本期.流程节点 != 空)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -749,11 +749,24 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>可用函数</t>
+          <t>空值</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>可用函数</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
         </is>
@@ -895,32 +908,32 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>为空</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
+          <t>= 空</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>本期不再上会, 清掉状态 (清空 = 写成空值; - 才是不改)</t>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>本期不再上会 (= 空 即判空, 也可写 为空), 清掉状态 (清空 = 写成空值, 也可写 空; - 才是不改)</t>
         </is>
       </c>
     </row>
@@ -933,32 +946,32 @@
       <c r="B5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>酝酿中的岗位由人工维护, 不处理。首次命中 下命中即停, 后面的规则不再看这一行 (优先级 策略下会被 S5 改成 01-新增)</t>
         </is>
@@ -973,32 +986,32 @@
       <c r="B6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>类别与上期相同, 且拟任人或流程节点有变化。两行同一个规则ID = 同一条规则的两个「或」分支: 每行各格 AND, 行间 OR</t>
         </is>
@@ -1007,28 +1020,28 @@
     <row r="7">
       <c r="A7" s="14" t="n"/>
       <c r="B7" s="14" t="n"/>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>S3 的第二个分支。续行的优先级和输出留空 (或与首行相同), 规则ID 可以合并单元格</t>
         </is>
@@ -1043,32 +1056,32 @@
       <c r="B8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>类别与上期相同, 没有变化</t>
         </is>
@@ -1083,32 +1096,32 @@
       <c r="B9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>兜底: 前面都没命中的行 (有类别、不是酝酿、与上期不同) 都是新增</t>
         </is>
@@ -1254,27 +1267,27 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>类别为空, 清掉状态。期望格写 清空 = 期望该列为空 (留空是期望不变)</t>
         </is>
@@ -1286,19 +1299,19 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="12" t="n"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>S2 拦截, 状态保持空; 优先级 策略下会被 S5 改成 01-新增, 这条用例会失败</t>
         </is>
@@ -1310,47 +1323,47 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>类别相同, 拟任人变了 -&gt; 进展更新</t>
         </is>
@@ -1362,23 +1375,23 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>上期没有这个岗位 -&gt; 兜底新增</t>
         </is>
@@ -1390,15 +1403,15 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>清空本来就空的格, 无变化</t>
         </is>
@@ -1410,31 +1423,31 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>类别变了 -&gt; 重新计为新增</t>
         </is>
@@ -1446,47 +1459,47 @@
           <t>T7</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>类别相同, 流程节点变了 -&gt; S3 的第二个分支</t>
         </is>
@@ -1498,47 +1511,47 @@
           <t>T8</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>类别相同, 都没变 -&gt; 按计划进行</t>
         </is>
@@ -1550,35 +1563,35 @@
           <t>T9</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>上期拟任人为空、本期有 = 新任命, 算变化 (变量定义里显式写的那一支)</t>
         </is>
@@ -1590,39 +1603,39 @@
           <t>T10</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>两期拟任人都空不算变化: != 两侧有空值就不成立, 决策表与 YAML 一致</t>
         </is>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="匹配设置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,26 +532,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>设置项</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>匹配</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>重复键</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -559,102 +572,50 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>左表</t>
+          <t>本期</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>主表</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>本期岗位.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>被更新的表, 相对路径以本规则文件所在目录为基准</t>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.类别-会议</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>右表</t>
+          <t>上期</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>岗位编码</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>取第一条</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>上期岗位.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>参照表, 只读</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>左表别名</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>本期</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>规则里引用左表字段的前缀, 如 本期.类别-会议</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>右表别名</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>上期</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>规则里引用右表字段的前缀, 如 上期.类别-会议</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>匹配键</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>岗位编码</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>两表按此列对行</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>output/本期岗位_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>结果文件, 原表不动</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>参照表, 按 岗位编码 对齐到主表; 引用写 上期.类别-会议, 上期.存在 = 是否匹配到</t>
         </is>
       </c>
     </row>
@@ -664,6 +625,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>output/本期岗位_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>默认输出路径, 命令行 -o 可覆盖; 不写则是 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -777,7 +791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1136,7 +1150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -782,7 +782,7 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, 值2, ...)</t>
+          <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
       </c>
     </row>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="7">
     <fill>
@@ -66,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,39 +89,6 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -128,45 +96,47 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,9 +506,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -592,7 +562,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>上期</t>
@@ -613,7 +583,7 @@
           <t>上期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>参照表, 按 岗位编码 对齐到主表; 引用写 上期.类别-会议, 上期.存在 = 是否匹配到</t>
         </is>
@@ -633,9 +603,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -655,7 +625,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>输出</t>
@@ -666,7 +636,7 @@
           <t>output/本期岗位_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>默认输出路径, 命令行 -o 可覆盖; 不写则是 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
@@ -687,8 +657,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,30 +678,30 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>拟任人有变化</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>本期.拟任人 != 上期.拟任人 或 (上期.拟任人 == 空 且 本期.拟任人 != 空)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>!= 两侧有空值就不成立 (和单元格一样), 所以「上期没填、本期填了」要单独写一支; == 空 / != 空 就是判空</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>流程节点有变化</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>本期.流程节点 != 上期.流程节点 或 (上期.流程节点 == 空 且 本期.流程节点 != 空)</t>
         </is>
@@ -760,27 +730,27 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="47" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
       <c r="B7" s="3" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -802,12 +772,12 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -816,7 +786,7 @@
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
@@ -828,314 +798,314 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>本期.类别-会议</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>拟任人有变化</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>流程节点有变化</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>= 空</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>本期不再上会 (= 空 即判空, 也可写 为空), 清掉状态 (清空 = 写成空值, 也可写 空; - 才是不改)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>酝酿中的岗位由人工维护, 不处理。首次命中 下命中即停, 后面的规则不再看这一行 (优先级 策略下会被 S5 改成 01-新增)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>类别与上期相同, 且拟任人或流程节点有变化。两行同一个规则ID = 同一条规则的两个「或」分支: 每行各格 AND, 行间 OR</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n"/>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>S3 的第二个分支。续行的优先级和输出留空 (或与首行相同), 规则ID 可以合并单元格</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>类别与上期相同, 没有变化</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>兜底: 前面都没命中的行 (有类别、不是酝酿、与上期不同) 都是新增</t>
         </is>
@@ -1159,497 +1129,497 @@
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="64" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>本期.类别-会议</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>本期.状态-会议</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>本期.拟任人</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>上期.拟任人</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>本期.流程节点</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>上期.流程节点</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>类别为空, 清掉状态。期望格写 清空 = 期望该列为空 (留空是期望不变)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="n"/>
-      <c r="I4" s="12" t="n"/>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>S2 拦截, 状态保持空; 优先级 策略下会被 S5 改成 01-新增, 这条用例会失败</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>类别相同, 拟任人变了 -&gt; 进展更新</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>上期没有这个岗位 -&gt; 兜底新增</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>清空本来就空的格, 无变化</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>类别变了 -&gt; 重新计为新增</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>类别相同, 流程节点变了 -&gt; S3 的第二个分支</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>类别相同, 都没变 -&gt; 按计划进行</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>上期拟任人为空、本期有 = 新任命, 算变化 (变量定义里显式写的那一支)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>两期拟任人都空不算变化: != 两侧有空值就不成立, 决策表与 YAML 一致</t>
         </is>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -628,17 +628,61 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>output/本期岗位_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>默认输出路径, 命令行 -o 可覆盖; 不写则是 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>拼接分隔符</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>命中策略 多条拼接 用的分隔符, 留空为 /。本表策略是 首次命中, 填了会报错</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
         </is>
       </c>
     </row>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="输入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="设置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="变量定义" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="决策表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="测试" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="设置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="变量定义" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="决策表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,12 +42,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,19 +94,19 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,7 +121,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,11 +501,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -515,75 +514,117 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>基准日期</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>output/本期岗位_更新后.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>可用设置项</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。下面「名称 / 匹配」那一行起是输入表</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>本期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.类别-会议</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>上期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>参照表, 按 岗位编码 对齐到主表; 引用写 上期.类别-会议, 上期.存在 = 是否匹配到</t>
         </is>
@@ -595,103 +636,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>设置项</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>基准日期</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>output/本期岗位_更新后.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>拼接分隔符</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>命中策略 多条拼接 用的分隔符, 留空为 /。本表策略是 首次命中, 填了会报错</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>可用设置项</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>只认上面三个, 写别的加载时报错 (不会静默忽略); 只读 A 列 (设置项) 和 B 列 (值), B 列留空 = 取默认值; 本列是说明, 不参与解析</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -706,24 +650,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>拟任人有变化</t>
         </is>
@@ -740,7 +684,7 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>流程节点有变化</t>
         </is>
@@ -750,32 +694,32 @@
           <t>本期.流程节点 != 上期.流程节点 或 (上期.流程节点 == 空 且 本期.流程节点 != 空)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>同上。两期都空不算变化</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="1" t="n"/>
       <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
@@ -788,7 +732,7 @@
       </c>
     </row>
     <row r="7" ht="47" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
@@ -805,7 +749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -825,17 +769,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>每行只听优先级数字最小的那条命中规则, 命中即停; 同优先级按行序。输出格 清空 = 写成空值, - = 不改</t>
         </is>
@@ -1109,7 +1053,7 @@
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>类别与上期相同, 没有变化</t>
         </is>
@@ -1164,7 +1108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1391,7 +1335,7 @@
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>类别相同, 拟任人变了 -&gt; 进展更新</t>
         </is>
@@ -1419,7 +1363,7 @@
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>上期没有这个岗位 -&gt; 兜底新增</t>
         </is>
@@ -1439,7 +1383,7 @@
       <c r="G7" s="13" t="n"/>
       <c r="H7" s="13" t="n"/>
       <c r="I7" s="14" t="n"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>清空本来就空的格, 无变化</t>
         </is>
@@ -1475,7 +1419,7 @@
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>类别变了 -&gt; 重新计为新增</t>
         </is>
@@ -1527,7 +1471,7 @@
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>类别相同, 流程节点变了 -&gt; S3 的第二个分支</t>
         </is>
@@ -1579,7 +1523,7 @@
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>类别相同, 都没变 -&gt; 按计划进行</t>
         </is>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -501,130 +501,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30.4" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="15.8" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>基准日期</t>
+          <t>设置项</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
+          <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>output/本期岗位_更新后.xlsx</t>
+          <t>基准日期</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
+          <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>可用设置项</t>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>output/本期岗位_更新后.xlsx</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>只认 基准日期 / 输出, 写别的加载时报错 (不会静默忽略); B 列留空 = 取默认值。下面「名称 / 匹配」那一行起是输入表</t>
+          <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>输入表</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>本期</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>主表</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>本期岗位.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.类别-会议</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>本期</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>主表</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>本期岗位.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.类别-会议</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>上期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>参照表, 按 岗位编码 对齐到主表; 引用写 上期.类别-会议, 上期.存在 = 是否匹配到</t>
         </is>
@@ -644,7 +656,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17.4" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
@@ -758,13 +770,13 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="19.2" customWidth="1" min="4" max="4"/>
+    <col width="15.2" customWidth="1" min="5" max="5"/>
+    <col width="17.4" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -909,7 +921,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="47" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>S2</t>
@@ -949,7 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="47" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>S3</t>
@@ -1118,14 +1130,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="17.2" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16.2" customWidth="1" min="7" max="7"/>
+    <col width="16.2" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>

--- a/examples/status-machine/规则_决策表.xlsx
+++ b/examples/status-machine/规则_决策表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,15 +30,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font/>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -66,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -88,52 +100,107 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,138 +578,154 @@
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>设置项</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>每行一项: A 列名字 / B 列值 / 再往右是说明; 只认 基准日期 / 输出, 写别的加载时报错; B 列留空 = 取默认值</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>基准日期</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>天数差 / N天 等日期计算用的「今天」, 日期格或 2026-10-19 文本都行。留空取运行当天 (本表没有日期计算, 所以留空)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="n"/>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>output/本期岗位_更新后.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>默认输出路径, 相对本规则文件所在目录, 命令行 -o 可覆盖。留空为 output/&lt;主表文件名&gt;_更新后.xlsx</t>
         </is>
       </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4"/>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>输入表</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>下一行是列名, 之后每行声明一个输入: 名称 = 规则里的前缀; 匹配 = 主表写 主表, 其它写对齐到主表的键; 文件 = 默认文件 (命令行 -i 可覆盖)。输入表下面不要再写别的</t>
         </is>
       </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>匹配</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>重复键</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>文件</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>本期</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>本期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>被更新的表: 输出的行就是它的行。规则里引用它的列写 本期.类别-会议</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>上期</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>岗位编码</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>取第一条</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>上期岗位.xlsx</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>参照表, 按 岗位编码 对齐到主表; 引用写 上期.类别-会议, 上期.存在 = 是否匹配到</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C5:E5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -662,95 +745,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>变量</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>定义</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>拟任人有变化</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>本期.拟任人 != 上期.拟任人 或 (上期.拟任人 == 空 且 本期.拟任人 != 空)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>!= 两侧有空值就不成立 (和单元格一样), 所以「上期没填、本期填了」要单独写一支; == 空 / != 空 就是判空</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>流程节点有变化</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>本期.流程节点 != 上期.流程节点 或 (上期.流程节点 == 空 且 本期.流程节点 != 空)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>同上。两期都空不算变化</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>连接词</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>且 / 或 / 非 (也认 and / or / not), 两侧留空格; 可用括号分组</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>空值</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>x == 空 / x != 空 判空 (也认 为空(x) / 非空(x)); 空 只能和 == / != 搭配, 不能参与大小比较和运算</t>
         </is>
       </c>
     </row>
     <row r="7" ht="47" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>可用函数</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>abs  round  天数差(晚, 早)  非空(x)  为空(x)  属于(x, 值1, ...)  包含 / 不包含 / 开头是 / 开头不是 / 结尾是 / 结尾不是 (x, 文本1, ...)  拼接(a, b, ...)  数字(x)  如果(条件, 真值, 假值)</t>
         </is>
@@ -781,339 +864,345 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>首次命中</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>每行只听优先级数字最小的那条命中规则, 命中即停; 同优先级按行序。输出格 清空 = 写成空值, - = 不改</t>
         </is>
       </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>输出</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>规则ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>本期.类别-会议</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>拟任人有变化</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>流程节点有变化</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>= 空</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>本期不再上会 (= 空 即判空, 也可写 为空), 清掉状态 (清空 = 写成空值, 也可写 空; - 才是不改)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="47" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>酝酿中的岗位由人工维护, 不处理。首次命中 下命中即停, 后面的规则不再看这一行 (优先级 策略下会被 S5 改成 01-新增)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="47" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>类别与上期相同, 且拟任人或流程节点有变化。两行同一个规则ID = 同一条规则的两个「或」分支: 每行各格 AND, 行间 OR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>S3 的第二个分支。续行的优先级和输出留空 (或与首行相同), 规则ID 可以合并单元格</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>= 本期.类别-会议</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>类别与上期相同, 没有变化</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>兜底: 前面都没命中的行 (有类别、不是酝酿、与上期不同) 都是新增</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C1:H1"/>
     <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1142,484 +1231,484 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>期望</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>用例</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>本期.类别-会议</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>本期.状态-会议</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>上期.类别-会议</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>本期.拟任人</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>上期.拟任人</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>本期.流程节点</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>上期.流程节点</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>状态-会议</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="13" t="n"/>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>清空</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>类别为空, 清掉状态。期望格写 清空 = 期望该列为空 (留空是期望不变)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="14" t="n"/>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>S2 拦截, 状态保持空; 优先级 策略下会被 S5 改成 01-新增, 这条用例会失败</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>类别相同, 拟任人变了 -&gt; 进展更新</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>上期没有这个岗位 -&gt; 兜底新增</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>清空本来就空的格, 无变化</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>近2个月酝酿及上会计划</t>
         </is>
       </c>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>类别变了 -&gt; 重新计为新增</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>T7</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>类别相同, 流程节点变了 -&gt; S3 的第二个分支</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>T8</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>周七</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>公司审批</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>类别相同, 都没变 -&gt; 按计划进行</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>T9</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>02-进展更新</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>上期拟任人为空、本期有 = 新任命, 算变化 (变量定义里显式写的那一支)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>01-新增</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>变动通报</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>部门评审</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>03-按计划进行</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>两期拟任人都空不算变化: != 两侧有空值就不成立, 决策表与 YAML 一致</t>
         </is>
